--- a/real_data/cp_test_random_seeds_2para_10k.xlsx
+++ b/real_data/cp_test_random_seeds_2para_10k.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BNU\BA4\毕业论文\LTRC-changepoint\real_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBD2F55-D845-4D9B-86C6-5A3AD51C2A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8596EE4-0A37-4D13-96A5-99514BED584A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="1550" windowWidth="13450" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="570" yWindow="2420" windowWidth="13450" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -7397,8 +7397,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D501">
-    <sortCondition ref="C1:C501"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D502">
+    <sortCondition ref="C1:C502"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
